--- a/docs/演示导入模板-合作协议.xlsx
+++ b/docs/演示导入模板-合作协议.xlsx
@@ -22,10 +22,11 @@
     <t>填写说明：
 * 必填列。
 协议类型：文本，选填
+协议状态：草稿 / 生效中 / 已失效 / 已续签 / 已终止（或 draft / active / expired / renewed / terminated），默认为 草稿
 开始日期 / 结束日期：格式 YYYY-MM-DD，选填
-状态：草稿 / 生效中 / 已失效 / 已续签 / 已终止（或 draft / active / expired / renewed / terminated），默认为 草稿
-关联归属项目：项目名称，选填，多值用中文分号「；」分隔，需与系统「合作项目」中的项目名称一致
-关联合作企业：企业名称，选填，多值用中文分号「；」分隔，需与系统「合作企业」中的企业名称一致
+内容：文本，选填
+合作企业：企业名称，选填，多值用中文分号「；」分隔，需与系统「合作企业」中的企业名称一致（按名称自动关联）
+关联项目：项目名称，选填，多值用中文分号「；」分隔，需与系统「合作项目」中的项目名称一致（按名称自动关联）
 公开显示：是 / 否，选填，默认为 否</t>
   </si>
   <si>
@@ -35,22 +36,22 @@
     <t>协议类型</t>
   </si>
   <si>
+    <t>协议状态</t>
+  </si>
+  <si>
     <t>开始日期</t>
   </si>
   <si>
     <t>结束日期</t>
   </si>
   <si>
-    <t>状态</t>
-  </si>
-  <si>
     <t>内容</t>
   </si>
   <si>
-    <t>关联归属项目</t>
-  </si>
-  <si>
-    <t>关联合作企业</t>
+    <t>合作企业</t>
+  </si>
+  <si>
+    <t>关联项目</t>
   </si>
   <si>
     <t>公开显示</t>
@@ -62,24 +63,24 @@
     <t>战略合作协议</t>
   </si>
   <si>
+    <t>生效中</t>
+  </si>
+  <si>
     <t>2026-03-01</t>
   </si>
   <si>
     <t>2028-02-29</t>
   </si>
   <si>
-    <t>生效中</t>
-  </si>
-  <si>
     <t>双方就新能源汽车充电桩关键技术联合研发达成战略合作，明确研发投入、成果归属与人才培养安排，合作期内共建联合实验室并每年输送实习实训岗位。</t>
   </si>
   <si>
+    <t>南京云驰新能源科技有限公司</t>
+  </si>
+  <si>
     <t>新能源汽车充电桩联合研发项目</t>
   </si>
   <si>
-    <t>南京云驰新能源科技有限公司</t>
-  </si>
-  <si>
     <t>是</t>
   </si>
   <si>
@@ -98,34 +99,34 @@
     <t>校企共建智能制造实训基地，企业投入产线与设备，学校提供场地与师资，共同开展实践教学、职工培训与技能鉴定。</t>
   </si>
   <si>
+    <t>苏州华芯智能制造有限公司</t>
+  </si>
+  <si>
     <t>智能制造实训基地共建项目</t>
   </si>
   <si>
-    <t>苏州华芯智能制造有限公司</t>
-  </si>
-  <si>
     <t>智慧教育装备技术服务协议</t>
   </si>
   <si>
     <t>技术服务协议</t>
   </si>
   <si>
+    <t>已续签</t>
+  </si>
+  <si>
     <t>2025-09-01</t>
   </si>
   <si>
     <t>2026-08-31</t>
   </si>
   <si>
-    <t>已续签</t>
-  </si>
-  <si>
     <t>企业为学校智慧教育装备提供技术支持与课程共建服务，学校协助企业开展产品教学化改造与师资培训。</t>
   </si>
   <si>
+    <t>无锡智联教育装备有限公司</t>
+  </si>
+  <si>
     <t>智慧教育装备课程开发项目</t>
-  </si>
-  <si>
-    <t>无锡智联教育装备有限公司</t>
   </si>
   <si>
     <t>否</t>
@@ -460,14 +461,14 @@
   <cols>
     <col customWidth="true" max="1" min="1" width="36"/>
     <col customWidth="true" max="2" min="2" width="22"/>
-    <col customWidth="true" max="4" min="3" width="16"/>
-    <col customWidth="true" max="5" min="5" width="20"/>
+    <col customWidth="true" max="3" min="3" width="20"/>
+    <col customWidth="true" max="5" min="4" width="16"/>
     <col customWidth="true" max="6" min="6" width="50"/>
     <col customWidth="true" max="8" min="7" width="44"/>
     <col customWidth="true" max="9" min="9" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="272" customHeight="true">
+    <row r="1" ht="304" customHeight="true">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -546,13 +547,13 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
